--- a/affiliate_data/สินค้าขายดี.xlsx
+++ b/affiliate_data/สินค้าขายดี.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>ไม้เซลฟี่บลูทูธ รุ่น K28P หมุนได้ 360 องศา พร้อมรีโมทบลูทูธ ยืดได้1.75ซม.ขาตั้งTripod พร้อมส่ง</v>
+        <v>ครีมโสมไฮยา สูตรเข้มข้น ( Intensive Active Ginseng Hya Night Cream)</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7rd63-m70pki5sxt3db3.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81zti-moxumfxycp357d.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>132.00</v>
+        <v>272.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 30พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/22390716846</v>
+        <v>https://shopee.co.th/product/0/23758244422</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/2BCIORE2pV</v>
+        <v>https://s.shopee.co.th/2VpWwxSB7R</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -480,37 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>adidas Football Liverpool FC 25/26 Home Jersey Men Red JV6423</v>
+        <v>ไม้เซลฟี่บลูทูธ รุ่น K28P หมุนได้ 360 องศา พร้อมรีโมทบลูทูธ ยืดได้1.75ซม.ขาตั้งTripod พร้อมส่ง</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823rg-mozkz8y7hngh5f.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-7rd63-m70pki5sxt3db3.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>2175.00</v>
+        <v>141.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/57752875499</v>
+        <v>https://shopee.co.th/product/0/22390716846</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/2g8YzMJyhA</v>
+        <v>https://s.shopee.co.th/30lnXsX9Lw</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -521,10 +521,10 @@
         <v>TOTORI หมอน รุ่น คลาวด์(Cloud model) , หมอนหนุน</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m7dtemqzvjru7c.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasl-m7dtemqzvjru7c.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>124.00</v>
+        <v>125.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -533,7 +533,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -542,7 +542,7 @@
         <v>https://shopee.co.th/product/0/28979758342</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/17noSeEeX</v>
+        <v>https://s.shopee.co.th/AAEy53EnsA</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>ใหม่ ! Oriental Princess ครีมทาผิว Moisturising Body Lotion 390 ml</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mo95qr9hd6o5aa.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztd-mo95qr9hd6o5aa.webp</v>
       </c>
       <c r="D5" t="str">
         <v>148.00</v>
@@ -580,7 +580,7 @@
         <v>https://shopee.co.th/product/0/7578431882</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/5L9KAGRQPk</v>
+        <v>https://s.shopee.co.th/7fXd6SWyzB</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>รองเท้าแตะ แบรนด์ MARCO รุ่น G1005 คาดเข็มขัด หนังนิ่ม</v>
+        <v>[Best Seller] Paloy - PL2360 Camellia Top เสื้อดอกคามิเลีย เสื้อแขนยาว ทรงเข้ารูป ปลายแขนแต่งดอกคามิเลีย</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7ra32-mbi09g90wacl3d.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81zto-mo97h5l1bs3q29.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>167.00</v>
+        <v>490.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>72</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/26288089781</v>
+        <v>https://shopee.co.th/product/0/27832497926</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/110L0IqEw2</v>
+        <v>https://s.shopee.co.th/6ff5ucfwhL</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น</v>
+        <v>แชมพูปิดผมขาวหอมเกศ พร้อมบำรุงเส้นผม 990 บาท (แบบขวด 300 มล.)</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mos57zj9wmq7bb.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>489.00</v>
+        <v>506.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 70พัน+ ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/22414045290</v>
+        <v>https://shopee.co.th/product/0/17909604787</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/2LViakttXG</v>
+        <v>https://s.shopee.co.th/3Vi48o02n1</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -670,31 +670,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>[ลด 50%] GQ Cool Tech กางเกงในไข่เย็น ของแท้ 100% ใส่สบาย ระบายอากาศ ไข่ไม่เหนียวเหนอะหนะ</v>
+        <v>PRIVACY ONLY CAP (Limited Edition)</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mdyso1l1mbcz05.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztm-moxolsaaeh3416.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>187.00</v>
+        <v>990.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>63</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 100พัน+ ชิ้น</v>
+        <v>ขายได้ 9พัน+ ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/23525917652</v>
+        <v>https://shopee.co.th/product/0/42960214119</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/7VDokFjv1Z</v>
+        <v>https://s.shopee.co.th/1gGPxRFxbE</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>แชมพูปิดผมขาวหอมเกศ พร้อมบำรุงเส้นผม 990 บาท (แบบขวด 300 มล.)</v>
+        <v>[ลด 50%] GQ Cool Tech กางเกงในไข่เย็น ของแท้ 100% ใส่สบาย ระบายอากาศ ไข่ไม่เหนียวเหนอะหนะ</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mos57zj9wmq7bb.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztk-mdyso1l1mbcz05.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>506.00</v>
+        <v>187.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 70พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/17909604787</v>
+        <v>https://shopee.co.th/product/0/23525917652</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/7pqf8rqclS</v>
+        <v>https://s.shopee.co.th/Ll2MzThMP</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -746,31 +746,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>[Best Seller] Paloy - PL2360 Camellia Top เสื้อดอกคามิเลีย เสื้อแขนยาว ทรงเข้ารูป ปลายแขนแต่งดอกคามิเลีย</v>
+        <v>mvp sport ชุดกีฬาทูพีช กางเกงขาสั้น+ชุดกีฬาแขนสั้น ใส่ได้ทั้งชายและหญิง เหมาะสำหรับน้ำหนัก 40kg-110kg</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mo97h5l1bs3q29.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m2kqhy2g61771f.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>490.00</v>
+        <v>132.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>17</v>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 50พัน+ ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/27832497926</v>
+        <v>https://shopee.co.th/product/0/27606542953</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/8KmvjmzNP4</v>
+        <v>https://s.shopee.co.th/7fXd6TF7Kq</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -784,31 +784,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>mvp sprot เสื้อกีฬา เสื้อรัดรูปแขนยาวออกกำลังกาย แจ็คเก็ตแขนยาวมีซิปรูด เสื้อสปอร์ตแขนยาว แจ็คเก็ตกันแดด ป้องกันรังสียูว</v>
+        <v>ROCKER WATERPROOF NANO สเปรย์กันน้ำ กันแดด กันฝุ่น รองเท้า กระเป๋า หมวก สเปรย์กันน้ำ กันสิ่งสกปรก สเปรย์กันน้ำรองเท้า</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7rdy3-mdhaxs8drqhw03.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7r98x-lqxk8zz1ysfi1b.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>139.00</v>
+        <v>183.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 30พัน+ ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/21001732437</v>
+        <v>https://shopee.co.th/product/0/24710836004</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/AAEZv9zGtc</v>
+        <v>https://s.shopee.co.th/1LdZYphQDH</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -822,37 +822,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>[บอสหนุ่ม] ยาสีฟันขิงขิง 1แถม1 ยาสีฟันสมุนไพร ลดกลิ่นปาก ฟันขาว ฟันแข็งแรง สินค้าจากบริษัทโดยตรง พร้อมจัดส่ง</v>
+        <v>🔥เสื้อกันฝนรุ่นหนา+แถมกระเป๋าพกพา🔥หนา ทนทาน📣 พร้อมส่ง 📣สต๊อกจริง📣รับประกันความคุ้ม100% สส</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-22090-obf5vp7h6xhved.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m6s568lain0797.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>290.00</v>
+        <v>186.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 5พัน+ ชิ้น</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/16086302672</v>
+        <v>https://shopee.co.th/product/0/22670266015</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/1BJlCccgqJ</v>
+        <v>https://s.shopee.co.th/70HwJFUr2O</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -860,37 +860,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>[ กด 2 ชิ้นเพื่อรับโปร 1 แถม 2 แถมหลังบ้านอัตโนมัติ ] MAGIC LIP OIL เมจิก ลิปออยล์ 3.5 กรัม</v>
+        <v>รองเท้าแตะ แบรนด์ MARCO รุ่น G1005 คาดเข็มขัด หนังนิ่ม</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mowteyfclf63d6.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-7ra32-mbi09g90wacl3d.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>199.00</v>
+        <v>167.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 100พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/25808041101</v>
+        <v>https://shopee.co.th/product/0/26288089781</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/17noTtVOT</v>
+        <v>https://s.shopee.co.th/AAEy54SM4R</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -898,31 +898,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Life Plus โพรไบโอ18 Life Plus ProBio18 Probiotic 2 กรัม ชนิดกรอกปาก(LPCAD)</v>
+        <v>mvp sport กางเกงวอร์มสตรีเอวสูงกางเกงโยคะเลกกิ้ง เป้าสามเหลี่ยม แบบไร้ตะเข็บหน้าเป้าไม่ยิ้ม</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhpurrwf2adi2f.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-md07yr981fr416.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>518.00</v>
+        <v>78.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/25613687442</v>
+        <v>https://shopee.co.th/product/0/13879902670</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/AUrQJmLrDP</v>
+        <v>https://s.shopee.co.th/18ByODaD0</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -936,37 +936,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>สบู่เฟย์ด้า ของแท้ FayDa planktonsoap สบู่รักษาสิว ขนาด 50 กรัม</v>
+        <v>โปรพิเศษ🔥สครับสปาบ้านทุ่ง 2 กป. ✨299 บาท สินค้าแท้ 100%✨</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m9xtvc28jzse8b.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mpdbdc780q30f2.webp</v>
       </c>
       <c r="D15" t="str">
-        <v>109.00</v>
+        <v>229.00</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>https://shopee.co.th/product/0/25059198086</v>
+        <v>https://shopee.co.th/product/0/25978598917</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/3Vhfyutix2</v>
+        <v>https://s.shopee.co.th/8pjaUcokqa</v>
       </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -974,31 +974,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>GQ Everyday Sport Polo เสื้อโปโล สไตล์สปอร์ต ผ้าใส่สบาย ระบายอากาศดี</v>
+        <v>(บลัชฉ่ำคุมมัน) BWB Blush in a Rush</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-mbp0n7oq2zmv5d.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztk-mpkz0ay83n5tef.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>265.00</v>
+        <v>488.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 70พัน+ ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/28126669065</v>
+        <v>https://shopee.co.th/product/0/25019295485</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/2BCIOT2vOS</v>
+        <v>https://s.shopee.co.th/W4SZJSnUE</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1012,37 +1012,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Hello Polo รองเท้าแฟชั่นผู้หญิง ดีไซน์เรียบง่าย พื้นหนานุ่ม กันลื่นและทนทาน คลายเมื่อยเท้า วัสดุ EVA แฟชั่นฤดูร้อนHP8067</v>
+        <v>ปากกา Capacitive แบบแอคทีฟ Universal iPhone Stylus เหมาะสําหรับ ipad Android โทรศัพท ์ แท ็ บเล ็ ตสไตลัส</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mop5uzmbsikh11.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/sg-11134201-7rdxc-lxgiayq11js633.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>159.00</v>
+        <v>91.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 710 ชิ้น</v>
+        <v>ขายได้ 50พัน+ ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/52809984572</v>
+        <v>https://shopee.co.th/product/0/27854767974</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/1LdBOwFAhJ</v>
+        <v>https://s.shopee.co.th/2LW6kgUPXr</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>GOOJODOQ Gfs007 Mini พัดลมพกพา 4000mah พัดลม Type C พร้อมจอแสดงผล พัดลมไอเย็น 100 ระดับ พัดลมมือถือ</v>
+        <v>เจลกำจัดมด ANTIANT แอนตี้แอนท์ [ของแท้จากร้าน Antiant Thailand]</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mh0c1qxjicr3a0.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztl-mibu5xev4kjq01.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>279.00</v>
+        <v>89.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/28841463764</v>
+        <v>https://shopee.co.th/product/0/21685245804</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/5L9KAI8XMI</v>
+        <v>https://s.shopee.co.th/9UzHHrBzqG</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1088,37 +1088,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>กางเกงออกกำลังกายขาสั้นผู้หญิง กางเกงโยคะ กางเกงขาสั้น</v>
+        <v>[ใหม่!!] WARRIX เสื้อโปโล รุ่น VIVIDUS POLO (WA-242PLACL30)</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mimgjwlflkw4c8.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mnmm1zeaeio658.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>140.00</v>
+        <v>379.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/53452439323</v>
+        <v>https://shopee.co.th/product/0/28402688576</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/7fXEwa9HLg</v>
+        <v>https://s.shopee.co.th/Ll2N0uaP5</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1126,31 +1126,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>[48 ฟรี 12] WHISKAS วิสกัส อาหารเปียกแมว ลูกแมว แมวโต แมวสูงวัย เลือกรสชาติได้ 80ก.</v>
+        <v>LOONNYSTORE เสื้อแขนยาวกระดุม รุ่น Zonry New Edition</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moxpql9rzqizdd.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mpkjmivwelfz69.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>864.00</v>
+        <v>590.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>20</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 30พัน+ ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/40117314945</v>
+        <v>https://shopee.co.th/product/0/44151771275</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/902cX2CrgK</v>
+        <v>https://s.shopee.co.th/BRcAi41JA</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1164,37 +1164,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>GQ Everyday T-Shirt เสื้อยืดผ้านุ่ม ยืดไม่ย้วย มี 17 สี คุณภาพเกินราคา ที่สุดแห่งความสบาย ระบายอากาศ ไม่มีป้ายคอ ไม่คัน</v>
+        <v>[แพ็คคู่] วาสลีน เฮลธี ไบรท์ ยูวี เอ็กซ์ตร้า ไบร์ทเทนนิ่ง+ กลูต้า เซราไมด์ โลชั่น 300 มล. VASELINE HEALTHY BRIGHT UV E</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rask-madn81zxp06u20.webp</v>
+        <v>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m13vjqfbtn3o49.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>164.00</v>
+        <v>219.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 200พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/18284848416</v>
+        <v>https://shopee.co.th/product/0/4065612614</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/BRE0nuOM6</v>
+        <v>https://s.shopee.co.th/3LOdwWzwJR</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
